--- a/docs/harness/wirelist/CAN-pinouts.xlsx
+++ b/docs/harness/wirelist/CAN-pinouts.xlsx
@@ -518,7 +518,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
@@ -558,13 +558,21 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>w_shd_can_trunk</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr"/>
+          <t>CAN screen trunk</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>splice sp_can_sh_clu (SP-CAN-SH-CLU)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
